--- a/게임UI프로토타입/펫파이팅_컨텐츠/기획서/데이터테이블/펫목록.xlsx
+++ b/게임UI프로토타입/펫파이팅_컨텐츠/기획서/데이터테이블/펫목록.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29CCBB0-954C-4369-B1E4-7555D09B1398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Desc" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Data" state="visible" r:id="rId5"/>
+    <sheet name="Desc" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -251,27 +255,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -293,42 +313,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe04030"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFff8060"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3a1010"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFa08030"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFd4b060"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1a1808"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7040b0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFa070e0"/>
+        <fgColor rgb="FFE04030"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8060"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3A1010"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA08030"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4B060"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1808"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7040B0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA070E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -343,7 +363,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFa0b0c0"/>
+        <fgColor rgb="FFA0B0C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -353,12 +373,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF40a060"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70d090"/>
+        <fgColor rgb="FF40A060"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70D090"/>
       </patternFill>
     </fill>
     <fill>
@@ -449,7 +469,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -785,9 +805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -795,7 +815,7 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="17.55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,7 +829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -823,7 +843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -837,7 +857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -851,7 +871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -865,7 +885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -879,7 +899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -893,7 +913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -907,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -921,7 +941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -935,7 +955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -949,7 +969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -963,7 +983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -977,7 +997,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -991,7 +1011,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -1006,15 +1026,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1029,7 +1050,7 @@
     <col min="14" max="14" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1073,7 +1094,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1096,28 +1117,28 @@
         <v>49</v>
       </c>
       <c r="H2" s="4">
+        <v>100</v>
+      </c>
+      <c r="I2" s="4">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4">
+        <v>20</v>
+      </c>
+      <c r="L2" s="4">
         <v>10</v>
       </c>
-      <c r="I2" s="4">
-        <v>3</v>
-      </c>
-      <c r="J2" s="4">
-        <v>2</v>
-      </c>
-      <c r="K2" s="4">
-        <v>2</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
       <c r="M2" s="4">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>4</v>
       </c>
@@ -1140,28 +1161,28 @@
         <v>56</v>
       </c>
       <c r="H3" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I3" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J3" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="L3" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M3" s="4">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>5</v>
       </c>
@@ -1184,28 +1205,28 @@
         <v>63</v>
       </c>
       <c r="H4" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I4" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J4" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K4" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L4" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M4" s="4">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>6</v>
       </c>
@@ -1228,28 +1249,28 @@
         <v>70</v>
       </c>
       <c r="H5" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I5" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K5" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L5" s="4">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="M5" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>7</v>
       </c>
@@ -1272,29 +1293,33 @@
         <v>76</v>
       </c>
       <c r="H6" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I6" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K6" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L6" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M6" s="4">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>77</v>
       </c>
     </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="I7" s="4"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>